--- a/DECISION/미장_드론_분석.xlsx
+++ b/DECISION/미장_드론_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-06</t>
+    <t>2025-12-10</t>
   </si>
   <si>
     <t>Archer Aviation Inc.</t>
@@ -501,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>8.6</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E2">
-        <v>57.8</v>
+        <v>61.8</v>
       </c>
       <c r="F2">
-        <v>10.4</v>
+        <v>11.82</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I2">
         <v>60</v>
       </c>
       <c r="J2">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K2">
-        <v>57.7</v>
+        <v>56.4</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>52.28493729186943</v>
+        <v>48.11568981226033</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,28 +548,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>15.26</v>
+        <v>15.32</v>
       </c>
       <c r="E3">
-        <v>56.4</v>
+        <v>60.7</v>
       </c>
       <c r="F3">
-        <v>5.75</v>
+        <v>10.76</v>
       </c>
       <c r="G3">
         <v>60</v>
       </c>
       <c r="H3">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I3">
         <v>60</v>
       </c>
       <c r="J3">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="K3">
-        <v>57.7</v>
+        <v>56.4</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>52.28493729186943</v>
+        <v>48.11568981226033</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_드론_분석.xlsx
+++ b/DECISION/미장_드론_분석.xlsx
@@ -64,16 +64,16 @@
     <t>2025-12-10</t>
   </si>
   <si>
+    <t>Joby Aviation, Inc.</t>
+  </si>
+  <si>
     <t>Archer Aviation Inc.</t>
   </si>
   <si>
-    <t>Joby Aviation, Inc.</t>
+    <t>JOBY</t>
   </si>
   <si>
     <t>ACHR</t>
-  </si>
-  <si>
-    <t>JOBY</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -501,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>8.550000000000001</v>
+        <v>15.44</v>
       </c>
       <c r="E2">
-        <v>61.8</v>
+        <v>61.9</v>
       </c>
       <c r="F2">
-        <v>11.82</v>
+        <v>11.64</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I2">
         <v>60</v>
       </c>
       <c r="J2">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="K2">
-        <v>56.4</v>
+        <v>55.9</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,28 +548,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>15.32</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="E3">
-        <v>60.7</v>
+        <v>62.8</v>
       </c>
       <c r="F3">
-        <v>10.76</v>
+        <v>12.81</v>
       </c>
       <c r="G3">
         <v>60</v>
       </c>
       <c r="H3">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I3">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="J3">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K3">
-        <v>56.4</v>
+        <v>54.3</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_드론_분석.xlsx
+++ b/DECISION/미장_드론_분석.xlsx
@@ -61,19 +61,19 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-10</t>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>Archer Aviation Inc.</t>
   </si>
   <si>
     <t>Joby Aviation, Inc.</t>
   </si>
   <si>
-    <t>Archer Aviation Inc.</t>
+    <t>ACHR</t>
   </si>
   <si>
     <t>JOBY</t>
-  </si>
-  <si>
-    <t>ACHR</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -501,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>15.44</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E2">
-        <v>61.9</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F2">
-        <v>11.64</v>
+        <v>-3.49</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H2">
         <v>63</v>
       </c>
       <c r="I2">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="J2">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="K2">
-        <v>55.9</v>
+        <v>58.4</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,28 +548,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>8.630000000000001</v>
+        <v>14.85</v>
       </c>
       <c r="E3">
-        <v>62.8</v>
+        <v>62.5</v>
       </c>
       <c r="F3">
-        <v>12.81</v>
+        <v>-2.69</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="I3">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="J3">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="K3">
-        <v>54.3</v>
+        <v>55.6</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_드론_분석.xlsx
+++ b/DECISION/미장_드론_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-15</t>
+    <t>2025-12-29</t>
   </si>
   <si>
     <t>Archer Aviation Inc.</t>
@@ -501,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>8.300000000000001</v>
+        <v>7.89</v>
       </c>
       <c r="E2">
-        <v>65.40000000000001</v>
+        <v>38.3</v>
       </c>
       <c r="F2">
-        <v>-3.49</v>
+        <v>0.9</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H2">
+        <v>56</v>
+      </c>
+      <c r="I2">
         <v>63</v>
-      </c>
-      <c r="I2">
-        <v>73</v>
       </c>
       <c r="J2">
         <v>70</v>
       </c>
       <c r="K2">
-        <v>58.4</v>
+        <v>49.8</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,28 +548,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>14.85</v>
+        <v>13.88</v>
       </c>
       <c r="E3">
-        <v>62.5</v>
+        <v>38.8</v>
       </c>
       <c r="F3">
-        <v>-2.69</v>
+        <v>0.22</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H3">
+        <v>56</v>
+      </c>
+      <c r="I3">
+        <v>60</v>
+      </c>
+      <c r="J3">
         <v>63</v>
       </c>
-      <c r="I3">
-        <v>66</v>
-      </c>
-      <c r="J3">
-        <v>80</v>
-      </c>
       <c r="K3">
-        <v>55.6</v>
+        <v>45.6</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_드론_분석.xlsx
+++ b/DECISION/미장_드론_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-29</t>
+    <t>2026-01-05</t>
   </si>
   <si>
     <t>Archer Aviation Inc.</t>
@@ -501,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>7.89</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="E2">
-        <v>38.3</v>
+        <v>43.9</v>
       </c>
       <c r="F2">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <v>30</v>
       </c>
       <c r="H2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I2">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="J2">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="K2">
-        <v>49.8</v>
+        <v>49.5</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,28 +548,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>13.88</v>
+        <v>14.36</v>
       </c>
       <c r="E3">
-        <v>38.8</v>
+        <v>41</v>
       </c>
       <c r="F3">
-        <v>0.22</v>
+        <v>0.63</v>
       </c>
       <c r="G3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H3">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="I3">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J3">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K3">
-        <v>45.6</v>
+        <v>46.7</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_드론_분석.xlsx
+++ b/DECISION/미장_드론_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-05</t>
+    <t>2026-01-07</t>
   </si>
   <si>
     <t>Archer Aviation Inc.</t>
@@ -501,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>8.130000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="E2">
-        <v>43.9</v>
+        <v>64.2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>14.55</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I2">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J2">
         <v>76</v>
       </c>
       <c r="K2">
-        <v>49.5</v>
+        <v>54.9</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>41.50472307187444</v>
+        <v>45.04298008974126</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,28 +548,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>14.36</v>
+        <v>16.3</v>
       </c>
       <c r="E3">
-        <v>41</v>
+        <v>64.5</v>
       </c>
       <c r="F3">
-        <v>0.63</v>
+        <v>20.38</v>
       </c>
       <c r="G3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H3">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="I3">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="J3">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K3">
-        <v>46.7</v>
+        <v>51.5</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>41.50472307187444</v>
+        <v>45.04298008974126</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_드론_분석.xlsx
+++ b/DECISION/미장_드론_분석.xlsx
@@ -522,7 +522,7 @@
         <v>76</v>
       </c>
       <c r="K2">
-        <v>54.9</v>
+        <v>55</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -569,7 +569,7 @@
         <v>76</v>
       </c>
       <c r="K3">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_드론_분석.xlsx
+++ b/DECISION/미장_드론_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-07</t>
+    <t>2026-01-08</t>
   </si>
   <si>
     <t>Archer Aviation Inc.</t>
@@ -501,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>8.82</v>
+        <v>8.42</v>
       </c>
       <c r="E2">
-        <v>64.2</v>
+        <v>56.2</v>
       </c>
       <c r="F2">
-        <v>14.55</v>
+        <v>11.52</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I2">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J2">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K2">
-        <v>55</v>
+        <v>56.3</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,28 +548,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>16.3</v>
+        <v>15.55</v>
       </c>
       <c r="E3">
-        <v>64.5</v>
+        <v>59.4</v>
       </c>
       <c r="F3">
-        <v>20.38</v>
+        <v>17.62</v>
       </c>
       <c r="G3">
         <v>60</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="I3">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="J3">
         <v>76</v>
       </c>
       <c r="K3">
-        <v>51.6</v>
+        <v>56.3</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_드론_분석.xlsx
+++ b/DECISION/미장_드론_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-08</t>
+    <t>2026-01-11</t>
   </si>
   <si>
     <t>Archer Aviation Inc.</t>
@@ -501,13 +501,13 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>8.42</v>
+        <v>8.81</v>
       </c>
       <c r="E2">
-        <v>56.2</v>
+        <v>63.9</v>
       </c>
       <c r="F2">
-        <v>11.52</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G2">
         <v>60</v>
@@ -516,13 +516,13 @@
         <v>60</v>
       </c>
       <c r="I2">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K2">
-        <v>56.3</v>
+        <v>57.1</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,28 +548,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>15.55</v>
+        <v>15.39</v>
       </c>
       <c r="E3">
-        <v>59.4</v>
+        <v>61.3</v>
       </c>
       <c r="F3">
-        <v>17.62</v>
+        <v>7.17</v>
       </c>
       <c r="G3">
         <v>60</v>
       </c>
       <c r="H3">
+        <v>66</v>
+      </c>
+      <c r="I3">
         <v>56</v>
       </c>
-      <c r="I3">
-        <v>63</v>
-      </c>
       <c r="J3">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K3">
-        <v>56.3</v>
+        <v>55.5</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_드론_분석.xlsx
+++ b/DECISION/미장_드론_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-11</t>
+    <t>2026-01-12</t>
   </si>
   <si>
     <t>Archer Aviation Inc.</t>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_드론_분석.xlsx
+++ b/DECISION/미장_드론_분석.xlsx
@@ -522,7 +522,7 @@
         <v>76</v>
       </c>
       <c r="K2">
-        <v>57.1</v>
+        <v>57.2</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -569,7 +569,7 @@
         <v>73</v>
       </c>
       <c r="K3">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_드론_분석.xlsx
+++ b/DECISION/미장_드론_분석.xlsx
@@ -61,19 +61,19 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-12</t>
+    <t>2026-01-13</t>
+  </si>
+  <si>
+    <t>Joby Aviation, Inc.</t>
   </si>
   <si>
     <t>Archer Aviation Inc.</t>
   </si>
   <si>
-    <t>Joby Aviation, Inc.</t>
+    <t>JOBY</t>
   </si>
   <si>
     <t>ACHR</t>
-  </si>
-  <si>
-    <t>JOBY</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -501,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>8.81</v>
+        <v>15.41</v>
       </c>
       <c r="E2">
-        <v>63.9</v>
+        <v>59.2</v>
       </c>
       <c r="F2">
-        <v>8.359999999999999</v>
+        <v>-3.93</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H2">
         <v>60</v>
       </c>
       <c r="I2">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="J2">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K2">
-        <v>57.2</v>
+        <v>58.6</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>50.56766494832259</v>
+        <v>47.98314273412904</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,28 +548,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>15.39</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="E3">
-        <v>61.3</v>
+        <v>60.7</v>
       </c>
       <c r="F3">
-        <v>7.17</v>
+        <v>3.5</v>
       </c>
       <c r="G3">
         <v>60</v>
       </c>
       <c r="H3">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="I3">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J3">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K3">
-        <v>55.6</v>
+        <v>56.4</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>50.56766494832259</v>
+        <v>47.98314273412904</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_드론_분석.xlsx
+++ b/DECISION/미장_드론_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-13</t>
+    <t>2026-01-14</t>
   </si>
   <si>
     <t>Joby Aviation, Inc.</t>
@@ -501,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>15.41</v>
+        <v>14.81</v>
       </c>
       <c r="E2">
-        <v>59.2</v>
+        <v>50.2</v>
       </c>
       <c r="F2">
-        <v>-3.93</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="G2">
         <v>50</v>
       </c>
       <c r="H2">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I2">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K2">
-        <v>58.6</v>
+        <v>55.9</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,28 +548,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>8.859999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="E3">
-        <v>60.7</v>
+        <v>51</v>
       </c>
       <c r="F3">
-        <v>3.5</v>
+        <v>-3.97</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="I3">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J3">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="K3">
-        <v>56.4</v>
+        <v>54.3</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_드론_분석.xlsx
+++ b/DECISION/미장_드론_분석.xlsx
@@ -61,19 +61,19 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-14</t>
+    <t>2026-01-17</t>
+  </si>
+  <si>
+    <t>Archer Aviation Inc.</t>
   </si>
   <si>
     <t>Joby Aviation, Inc.</t>
   </si>
   <si>
-    <t>Archer Aviation Inc.</t>
+    <t>ACHR</t>
   </si>
   <si>
     <t>JOBY</t>
-  </si>
-  <si>
-    <t>ACHR</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -501,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>14.81</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="E2">
-        <v>50.2</v>
+        <v>64.3</v>
       </c>
       <c r="F2">
-        <v>-9.140000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I2">
         <v>70</v>
       </c>
       <c r="J2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="K2">
-        <v>55.9</v>
+        <v>58.1</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,28 +548,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>8.470000000000001</v>
+        <v>15.43</v>
       </c>
       <c r="E3">
-        <v>51</v>
+        <v>62.5</v>
       </c>
       <c r="F3">
-        <v>-3.97</v>
+        <v>0.26</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H3">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="I3">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="J3">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="K3">
-        <v>54.3</v>
+        <v>54.1</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_드론_분석.xlsx
+++ b/DECISION/미장_드론_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-17</t>
+    <t>2026-01-19</t>
   </si>
   <si>
     <t>Archer Aviation Inc.</t>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_드론_분석.xlsx
+++ b/DECISION/미장_드론_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-19</t>
+    <t>2026-03-03</t>
   </si>
   <si>
     <t>Archer Aviation Inc.</t>
@@ -82,7 +82,7 @@
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>⚪ 중립 구간</t>
+    <t>🔴 강한 긴축 / 리스크</t>
   </si>
 </sst>
 </file>
@@ -501,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>8.859999999999999</v>
+        <v>7.52</v>
       </c>
       <c r="E2">
-        <v>64.3</v>
+        <v>52.8</v>
       </c>
       <c r="F2">
-        <v>0.57</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I2">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="J2">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="K2">
-        <v>58.1</v>
+        <v>49.3</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>40.44495449250464</v>
+        <v>20.49503599836755</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,28 +548,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>15.43</v>
+        <v>10.27</v>
       </c>
       <c r="E3">
-        <v>62.5</v>
+        <v>42.9</v>
       </c>
       <c r="F3">
-        <v>0.26</v>
+        <v>7.65</v>
       </c>
       <c r="G3">
+        <v>50</v>
+      </c>
+      <c r="H3">
         <v>60</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>63</v>
-      </c>
-      <c r="I3">
-        <v>60</v>
       </c>
       <c r="J3">
         <v>76</v>
       </c>
       <c r="K3">
-        <v>54.1</v>
+        <v>46.3</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>40.44495449250464</v>
+        <v>20.49503599836755</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_드론_분석.xlsx
+++ b/DECISION/미장_드론_분석.xlsx
@@ -61,25 +61,25 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-03</t>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>Joby Aviation, Inc.</t>
   </si>
   <si>
     <t>Archer Aviation Inc.</t>
   </si>
   <si>
-    <t>Joby Aviation, Inc.</t>
+    <t>JOBY</t>
   </si>
   <si>
     <t>ACHR</t>
   </si>
   <si>
-    <t>JOBY</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
-    <t>⛔ 관망하십시오.</t>
+    <t>🤏 바닥권 접근 구간입니다.</t>
   </si>
   <si>
     <t>🔴 강한 긴축 / 리스크</t>
@@ -501,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>7.52</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="E2">
-        <v>52.8</v>
+        <v>44.4</v>
       </c>
       <c r="F2">
-        <v>8.050000000000001</v>
+        <v>-5.07</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H2">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="I2">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J2">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="K2">
-        <v>49.3</v>
+        <v>36.7</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,16 +548,16 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>10.27</v>
+        <v>6.26</v>
       </c>
       <c r="E3">
-        <v>42.9</v>
+        <v>42.5</v>
       </c>
       <c r="F3">
-        <v>7.65</v>
+        <v>-12.08</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H3">
         <v>60</v>
@@ -566,10 +566,10 @@
         <v>63</v>
       </c>
       <c r="J3">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K3">
-        <v>46.3</v>
+        <v>29.5</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_드론_분석.xlsx
+++ b/DECISION/미장_드론_분석.xlsx
@@ -522,7 +522,7 @@
         <v>70</v>
       </c>
       <c r="K2">
-        <v>36.7</v>
+        <v>35.4</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -569,7 +569,7 @@
         <v>73</v>
       </c>
       <c r="K3">
-        <v>29.5</v>
+        <v>28.2</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_드론_분석.xlsx
+++ b/DECISION/미장_드론_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-09</t>
+    <t>2026-03-10</t>
   </si>
   <si>
     <t>Joby Aviation, Inc.</t>
@@ -79,10 +79,10 @@
     <t>Pattern</t>
   </si>
   <si>
-    <t>🤏 바닥권 접근 구간입니다.</t>
-  </si>
-  <si>
-    <t>🔴 강한 긴축 / 리스크</t>
+    <t>⛔ 관망하십시오.</t>
+  </si>
+  <si>
+    <t>🟠 하락 우위 (긴장 구간)</t>
   </si>
 </sst>
 </file>
@@ -501,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>9.550000000000001</v>
+        <v>10.04</v>
       </c>
       <c r="E2">
-        <v>44.4</v>
+        <v>50.7</v>
       </c>
       <c r="F2">
-        <v>-5.07</v>
+        <v>-2.24</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H2">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I2">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="J2">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="K2">
-        <v>35.4</v>
+        <v>50.9</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,28 +548,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>6.26</v>
+        <v>6.52</v>
       </c>
       <c r="E3">
-        <v>42.5</v>
+        <v>45.8</v>
       </c>
       <c r="F3">
-        <v>-12.08</v>
+        <v>-13.3</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="I3">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J3">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K3">
-        <v>28.2</v>
+        <v>42.1</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_드론_분석.xlsx
+++ b/DECISION/미장_드론_분석.xlsx
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_드론_분석.xlsx
+++ b/DECISION/미장_드론_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-10</t>
+    <t>2026-03-11</t>
   </si>
   <si>
     <t>Joby Aviation, Inc.</t>
@@ -82,7 +82,7 @@
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>🟠 하락 우위 (긴장 구간)</t>
+    <t>⚪ 중립 구간</t>
   </si>
 </sst>
 </file>
@@ -501,13 +501,13 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>10.04</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="E2">
-        <v>50.7</v>
+        <v>47.1</v>
       </c>
       <c r="F2">
-        <v>-2.24</v>
+        <v>1.23</v>
       </c>
       <c r="G2">
         <v>40</v>
@@ -516,13 +516,13 @@
         <v>66</v>
       </c>
       <c r="I2">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J2">
         <v>80</v>
       </c>
       <c r="K2">
-        <v>50.9</v>
+        <v>53</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,28 +548,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>6.52</v>
+        <v>6.32</v>
       </c>
       <c r="E3">
-        <v>45.8</v>
+        <v>41.1</v>
       </c>
       <c r="F3">
-        <v>-13.3</v>
+        <v>-5.95</v>
       </c>
       <c r="G3">
         <v>20</v>
       </c>
       <c r="H3">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="I3">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="J3">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="K3">
-        <v>42.1</v>
+        <v>43</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_드론_분석.xlsx
+++ b/DECISION/미장_드론_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-11</t>
+    <t>2026-03-12</t>
   </si>
   <si>
     <t>Joby Aviation, Inc.</t>
@@ -501,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>9.880000000000001</v>
+        <v>10.23</v>
       </c>
       <c r="E2">
-        <v>47.1</v>
+        <v>49.7</v>
       </c>
       <c r="F2">
-        <v>1.23</v>
+        <v>3.44</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I2">
         <v>70</v>
       </c>
       <c r="J2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="K2">
-        <v>53</v>
+        <v>55.5</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>43.44936356612781</v>
+        <v>41.74287521812095</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,28 +548,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>6.32</v>
+        <v>6.43</v>
       </c>
       <c r="E3">
-        <v>41.1</v>
+        <v>38.6</v>
       </c>
       <c r="F3">
-        <v>-5.95</v>
+        <v>-4.88</v>
       </c>
       <c r="G3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H3">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I3">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="J3">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K3">
-        <v>43</v>
+        <v>37.9</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>43.44936356612781</v>
+        <v>41.74287521812095</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_드론_분석.xlsx
+++ b/DECISION/미장_드론_분석.xlsx
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_드론_분석.xlsx
+++ b/DECISION/미장_드론_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-12</t>
+    <t>2026-04-08</t>
   </si>
   <si>
     <t>Joby Aviation, Inc.</t>
@@ -82,7 +82,7 @@
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>⚪ 중립 구간</t>
+    <t>🟢 상승 우위 (다소 완화)</t>
   </si>
 </sst>
 </file>
@@ -501,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>10.23</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="E2">
-        <v>49.7</v>
+        <v>27.7</v>
       </c>
       <c r="F2">
-        <v>3.44</v>
+        <v>5.54</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H2">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="I2">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="J2">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="K2">
-        <v>55.5</v>
+        <v>51.4</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,28 +548,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>6.43</v>
+        <v>5.34</v>
       </c>
       <c r="E3">
-        <v>38.6</v>
+        <v>31.1</v>
       </c>
       <c r="F3">
-        <v>-4.88</v>
+        <v>8.1</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I3">
+        <v>46</v>
+      </c>
+      <c r="J3">
         <v>56</v>
       </c>
-      <c r="J3">
-        <v>66</v>
-      </c>
       <c r="K3">
-        <v>37.9</v>
+        <v>47.4</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_드론_분석.xlsx
+++ b/DECISION/미장_드론_분석.xlsx
@@ -61,28 +61,28 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-04-08</t>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>Archer Aviation Inc.</t>
   </si>
   <si>
     <t>Joby Aviation, Inc.</t>
   </si>
   <si>
-    <t>Archer Aviation Inc.</t>
+    <t>ACHR</t>
   </si>
   <si>
     <t>JOBY</t>
   </si>
   <si>
-    <t>ACHR</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>🟢 상승 우위 (다소 완화)</t>
+    <t>⚪ 중립 구간</t>
   </si>
 </sst>
 </file>
@@ -501,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>8.380000000000001</v>
+        <v>6.41</v>
       </c>
       <c r="E2">
-        <v>27.7</v>
+        <v>57.5</v>
       </c>
       <c r="F2">
-        <v>5.54</v>
+        <v>14.46</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H2">
+        <v>46</v>
+      </c>
+      <c r="I2">
         <v>53</v>
-      </c>
-      <c r="I2">
-        <v>56</v>
       </c>
       <c r="J2">
         <v>56</v>
       </c>
       <c r="K2">
-        <v>51.4</v>
+        <v>53.9</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>66.57973643566133</v>
+        <v>59.14876667115259</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,28 +548,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>5.34</v>
+        <v>10.52</v>
       </c>
       <c r="E3">
-        <v>31.1</v>
+        <v>63.2</v>
       </c>
       <c r="F3">
-        <v>8.1</v>
+        <v>20.92</v>
       </c>
       <c r="G3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H3">
+        <v>46</v>
+      </c>
+      <c r="I3">
         <v>40</v>
       </c>
-      <c r="I3">
-        <v>46</v>
-      </c>
       <c r="J3">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="K3">
-        <v>47.4</v>
+        <v>48.7</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>66.57973643566133</v>
+        <v>59.14876667115259</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>

--- a/DECISION/미장_드론_분석.xlsx
+++ b/DECISION/미장_드론_분석.xlsx
@@ -61,28 +61,28 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-05-07</t>
+    <t>2026-06-07</t>
+  </si>
+  <si>
+    <t>Joby Aviation, Inc.</t>
   </si>
   <si>
     <t>Archer Aviation Inc.</t>
   </si>
   <si>
-    <t>Joby Aviation, Inc.</t>
+    <t>JOBY</t>
   </si>
   <si>
     <t>ACHR</t>
   </si>
   <si>
-    <t>JOBY</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>⚪ 중립 구간</t>
+    <t>🔴 강한 긴축 / 리스크</t>
   </si>
 </sst>
 </file>
@@ -501,28 +501,28 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>6.41</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="E2">
-        <v>57.5</v>
+        <v>42.8</v>
       </c>
       <c r="F2">
-        <v>14.46</v>
+        <v>-19.75</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H2">
+        <v>53</v>
+      </c>
+      <c r="I2">
+        <v>56</v>
+      </c>
+      <c r="J2">
         <v>46</v>
       </c>
-      <c r="I2">
-        <v>53</v>
-      </c>
-      <c r="J2">
-        <v>56</v>
-      </c>
       <c r="K2">
-        <v>53.9</v>
+        <v>35.3</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="N2">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O2" t="s">
         <v>22</v>
@@ -548,28 +548,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>10.52</v>
+        <v>5.54</v>
       </c>
       <c r="E3">
-        <v>63.2</v>
+        <v>40.3</v>
       </c>
       <c r="F3">
-        <v>20.92</v>
+        <v>-18.65</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="I3">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="J3">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="K3">
-        <v>48.7</v>
+        <v>32.3</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="N3">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>
